--- a/marque1.xlsx
+++ b/marque1.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fe2a256f1c22afb0/เอกสาร/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="8_{C63EB804-137A-4ABD-9E45-B770F4641F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBA20660-45B5-4572-81D5-67C947FF084A}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3B211D9F-2689-4DF9-A4A1-C977F4022225}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -320,9 +314,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="8" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -373,7 +367,7 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -443,7 +437,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -495,7 +489,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -689,24 +683,24 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68E8FD9A-C365-4AA4-AA1D-FB727CA00682}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="30.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="26.5546875" style="3" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="37.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -717,7 +711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -728,7 +722,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -739,7 +733,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="109.15" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -772,7 +766,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -794,7 +788,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -805,7 +799,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
@@ -838,7 +832,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>85</v>
       </c>
@@ -849,7 +843,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>35</v>
       </c>
@@ -860,7 +854,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="78" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>37</v>
       </c>
@@ -871,7 +865,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>40</v>
       </c>
@@ -882,7 +876,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="62.45" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>42</v>
       </c>
@@ -904,7 +898,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="62.45" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>46</v>
       </c>
@@ -926,7 +920,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>49</v>
       </c>
@@ -937,7 +931,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>52</v>
       </c>
@@ -948,7 +942,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>55</v>
       </c>
@@ -959,7 +953,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>58</v>
       </c>
@@ -970,7 +964,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>61</v>
       </c>
@@ -981,7 +975,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>64</v>
       </c>
@@ -992,7 +986,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="78" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>67</v>
       </c>
@@ -1003,7 +997,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>84</v>
       </c>
@@ -1014,7 +1008,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>72</v>
       </c>
@@ -1025,7 +1019,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>74</v>
       </c>
@@ -1036,7 +1030,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>77</v>
       </c>
@@ -1047,7 +1041,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>79</v>
       </c>
